--- a/ExcelTable/Monster.xlsx
+++ b/ExcelTable/Monster.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterDefinitions" sheetId="1" r:id="R8d6df80c983648bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterDefinitions" sheetId="1" r:id="Rafee47721dd34878"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -51,12 +51,37 @@
       <x:name val="Malgun Gothic"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF172033"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF334155"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -104,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -156,6 +181,19 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -406,6 +444,8 @@
     <x:col min="29" max="29" width="18.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="18.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="31" max="31" width="18.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="23.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="16.5" customHeight="1">
@@ -502,6 +542,12 @@
       <x:c r="AE1" s="7" t="str">
         <x:v>HitAnimationDurationSeconds</x:v>
       </x:c>
+      <x:c r="AF1" s="20" t="str">
+        <x:v>ContactSkillInfoIndex</x:v>
+      </x:c>
+      <x:c r="AG1" s="20" t="str">
+        <x:v>ActiveSkillInfoIndex</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="16.5" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -597,6 +643,12 @@
       <x:c r="AE2" s="9" t="str">
         <x:v>server</x:v>
       </x:c>
+      <x:c r="AF2" s="22" t="str">
+        <x:v>server</x:v>
+      </x:c>
+      <x:c r="AG2" s="22" t="str">
+        <x:v>server</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="12" t="str">
@@ -692,6 +744,12 @@
       <x:c r="AE3" s="12" t="str">
         <x:v>피격 행동을 잠그고 피격 애니메이션을 유지하는 시간입니다.</x:v>
       </x:c>
+      <x:c r="AF3" s="25" t="str">
+        <x:v>Skill.xlsx/SkillInfo의 접촉 피해 행 인덱스입니다.</x:v>
+      </x:c>
+      <x:c r="AG3" s="25" t="str">
+        <x:v>Skill.xlsx/SkillInfo의 능동 공격 행 인덱스입니다. CONTACT형은 비워둡니다.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="16.5" customHeight="1">
       <x:c r="A4" s="14" t="str">
@@ -787,6 +845,12 @@
       <x:c r="AE4" s="14" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="AF4" s="27" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AG4" s="27" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="16.5" customHeight="1">
       <x:c r="A5" s="17" t="n">
@@ -880,6 +944,10 @@
       <x:c r="AE5" s="17" t="n">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="AF5" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG5" s="29"/>
     </x:row>
     <x:row r="6" ht="16.5" customHeight="1">
       <x:c r="A6" s="17" t="n">
@@ -974,6 +1042,12 @@
       </x:c>
       <x:c r="AE6" s="17" t="n">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="AF6" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG6" s="29" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
